--- a/results/f1_prec_recall/Final-PrecRecallF1.xlsx
+++ b/results/f1_prec_recall/Final-PrecRecallF1.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11010"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sunwu/SW-Research/Time-Series-Library-main/0A-PaperResults/baselines/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A55598E-FB7F-7E44-A231-CD15C1E5A9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28940" windowHeight="13960" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="F1" sheetId="6" r:id="rId1"/>
-    <sheet name="Prec" sheetId="7" r:id="rId2"/>
-    <sheet name="Recall" sheetId="8" r:id="rId3"/>
+    <sheet name="F1V2" sheetId="9" r:id="rId1"/>
+    <sheet name="PrecV2" sheetId="10" r:id="rId2"/>
+    <sheet name="RecallV2" sheetId="11" r:id="rId3"/>
+    <sheet name="F1" sheetId="6" r:id="rId4"/>
+    <sheet name="Prec" sheetId="7" r:id="rId5"/>
+    <sheet name="Recall" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -20,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="40">
   <si>
     <t>F1</t>
   </si>
@@ -108,19 +115,71 @@
   <si>
     <t>Recall</t>
   </si>
+  <si>
+    <t>RANK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ours</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>AR</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KNeighborsTimeSeries</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TDE</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>best</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>second_best</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>best(Latex)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>second_best(Latex)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>行标签F1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>行标签Prec</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>行标签Recall</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1NN-DTW</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
+    <numFmt numFmtId="180" formatCode="0.0000"/>
+    <numFmt numFmtId="185" formatCode="0.0000_);[Red]\(0.0000\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +192,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
@@ -140,6 +200,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -147,12 +208,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -160,155 +223,45 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,198 +276,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD9E1F4"/>
+        <bgColor rgb="FFD9E1F4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -536,22 +315,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4" tint="0.39994506668294322"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,8 +323,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,227 +332,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF91AADF"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -804,102 +359,216 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="185" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="185" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -910,7 +579,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -938,154 +607,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1335,28 +890,3349 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA5443C-455B-9545-B90C-BFE82D40E837}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.6923076923077" customWidth="1"/>
-    <col min="2" max="2" width="14.3076923076923" customWidth="1"/>
-    <col min="3" max="3" width="12.6153846153846" customWidth="1"/>
-    <col min="4" max="4" width="15.0769230769231" customWidth="1"/>
-    <col min="5" max="5" width="14.6923076923077" customWidth="1"/>
-    <col min="6" max="6" width="23.1538461538462" customWidth="1"/>
-    <col min="7" max="7" width="8.69230769230769" customWidth="1"/>
-    <col min="8" max="8" width="10.9230769230769" customWidth="1"/>
-    <col min="9" max="9" width="10.4615384615385" customWidth="1"/>
-    <col min="10" max="10" width="10.3846153846154" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:11">
+    <row r="1" spans="1:12" ht="15">
+      <c r="A1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10">
+        <v>0.27726616081579902</v>
+      </c>
+      <c r="C2" s="10">
+        <v>0.679305762375366</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0.747910387887329</v>
+      </c>
+      <c r="E2" s="10">
+        <v>0.65077293955489302</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.98757895689331798</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.79933603850433399</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0.99672518743640803</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0.82085908046989298</v>
+      </c>
+      <c r="J2" s="10">
+        <v>0.49713928712129002</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0.90144669905706698</v>
+      </c>
+      <c r="L2">
+        <f>AVERAGE(B15:K15)</f>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="10">
+        <v>0.220070852704081</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.499042570250819</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.68895604999776605</v>
+      </c>
+      <c r="E3" s="10">
+        <v>7.0740688970944904E-2</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0.44004411394847498</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.98128619237566195</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0.25857529684943198</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0.68372430620975</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0.55045160528206105</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0.71743925539580899</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L11" si="0">AVERAGE(B16:K16)</f>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.316310412369391</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.52862869114214395</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0.64234461054287895</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.592338630774496</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.95162343092523405</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.68968892093388801</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.96278925837408202</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0.76813060178000503</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0.53876076687968799</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0.90221737422747295</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="10">
+        <v>0.26663132439257697</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.52730410489457502</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.74571820752081197</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.572111811228044</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.98168388653718797</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.80058105132783797</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.98753574790492404</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.82445357933125196</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0.46831909187677601</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0.753835175567792</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.29073577227273517</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.57067500892985179</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.72493891288925438</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.2115471937479696</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.98108378759964088</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.82865084752870888</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.99172665819929762</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.81740201121557376</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0.58096751010673875</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0.81885013476078006</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0.1824183605561138</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.65308690971068639</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.72135542912939543</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0.17486688598322536</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.9789362922646706</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.85454653626700916</v>
+      </c>
+      <c r="H7" s="11">
+        <v>0.9828727290650896</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0.74408063968173299</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0.48895707716201581</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0.88932688684096683</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0.25741847555931158</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.65062539590505419</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.7709838526833005</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0.37103606819473012</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0.97472720206864272</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.76596770386532376</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.99127503155808649</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.87724935912482116</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.56756598131930336</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0.91143019360755062</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.22097658784245677</v>
+      </c>
+      <c r="C9" s="11">
+        <v>0.66462362383851181</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0.65349938328817647</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.25541623005343861</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.952219721923519</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.85602225415079225</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0.97516894132790788</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0.83487624687807682</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0.50383186996268703</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0.84387281190927221</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="11">
+        <v>0.25543738512461739</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.65972467554470204</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.7327839683101135</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0.30413821619754877</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0.97677133604792732</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.83917072548919192</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0.98879723839801792</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0.90433576097473178</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0.54785946709863853</v>
+      </c>
+      <c r="K10" s="11">
+        <v>0.86900955914904876</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.30624058797410098</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.68185144713865298</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0.78178693490756501</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.3957097272176</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0.98279971823907286</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.83624225870210134</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0.99645590485548663</v>
+      </c>
+      <c r="I11" s="11">
+        <v>0.9241651782054463</v>
+      </c>
+      <c r="J11" s="11">
+        <v>0.58177143034170797</v>
+      </c>
+      <c r="K11" s="11">
+        <v>0.91932571995523382</v>
+      </c>
+      <c r="L11">
+        <f>AVERAGE(B24:K24)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <f>RANK(B2,B$2:B$11)</f>
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:K15" si="1">RANK(C2,C$2:C$11)</f>
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:K24" si="2">RANK(B3,B$2:B$11)</f>
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="9">
+        <f>MAX(B2:B11)</f>
+        <v>0.316310412369391</v>
+      </c>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:L27" si="3">MAX(C2:C11)</f>
+        <v>0.68185144713865298</v>
+      </c>
+      <c r="D27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.78178693490756501</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.65077293955489302</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.98757895689331798</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.98128619237566195</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.99672518743640803</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.9241651782054463</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.58177143034170797</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.91932571995523382</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="3"/>
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="6">
+        <f>LARGE(B2:B11,2)</f>
+        <v>0.30624058797410098</v>
+      </c>
+      <c r="C28" s="6">
+        <f t="shared" ref="C28:L28" si="4">LARGE(C2:C11,2)</f>
+        <v>0.679305762375366</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.7709838526833005</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.592338630774496</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.98279971823907286</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.85602225415079225</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.99645590485548663</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.90433576097473178</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.58096751010673875</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.91143019360755062</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="4"/>
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="45">
+      <c r="A30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="19" t="str">
+        <f>"\textbf{"&amp;TEXT(B27,"0.0000")&amp;"}"</f>
+        <v>\textbf{0.3163}</v>
+      </c>
+      <c r="C30" s="19" t="str">
+        <f t="shared" ref="C30:K30" si="5">"\textbf{"&amp;TEXT(C27,"0.0000")&amp;"}"</f>
+        <v>\textbf{0.6819}</v>
+      </c>
+      <c r="D30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.7818}</v>
+      </c>
+      <c r="E30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.6508}</v>
+      </c>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9876}</v>
+      </c>
+      <c r="G30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9813}</v>
+      </c>
+      <c r="H30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9967}</v>
+      </c>
+      <c r="I30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9242}</v>
+      </c>
+      <c r="J30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.5818}</v>
+      </c>
+      <c r="K30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9193}</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="45">
+      <c r="A31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="19" t="str">
+        <f>"\underline{"&amp;TEXT(B28,"0.0000")&amp;"}"</f>
+        <v>\underline{0.3062}</v>
+      </c>
+      <c r="C31" s="19" t="str">
+        <f t="shared" ref="C31:K31" si="6">"\underline{"&amp;TEXT(C28,"0.0000")&amp;"}"</f>
+        <v>\underline{0.6793}</v>
+      </c>
+      <c r="D31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.7710}</v>
+      </c>
+      <c r="E31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.5923}</v>
+      </c>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9828}</v>
+      </c>
+      <c r="G31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.8560}</v>
+      </c>
+      <c r="H31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9965}</v>
+      </c>
+      <c r="I31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9043}</v>
+      </c>
+      <c r="J31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.5810}</v>
+      </c>
+      <c r="K31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9114}</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DD3E94B-A14B-7049-8555-A1072A97E783}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15">
+      <c r="A1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0.28359879848487901</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0.67942171881000801</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0.74613839433554896</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.68257175690876104</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0.98779364707108597</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0.82084618281752997</v>
+      </c>
+      <c r="H2" s="9">
+        <v>0.99678790185553701</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0.84761896200514197</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0.49875547890118299</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0.90477839932413096</v>
+      </c>
+      <c r="L2">
+        <f>AVERAGE(B15:K15)</f>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0.21938231112155901</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.49920803343943598</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.73415331562364905</v>
+      </c>
+      <c r="E3" s="9">
+        <v>7.5630156366188694E-2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.52652096652332103</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.98373834829475304</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0.27726389300061599</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0.77051625003843405</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0.55473134759976805</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0.72784710260531404</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L10" si="0">AVERAGE(B16:K16)</f>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.31782325979094</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.52866837875986294</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.63177244175542502</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.62834450918373896</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.95565965864444502</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.72182839639486995</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.96450349299996396</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.81116794207215204</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.53893214682981005</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0.909807403683627</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.27603275741327099</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.52905857614019103</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.745557411646251</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.58807566770183095</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.98223218252518196</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.82038514623360503</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.98788009124023501</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.83238268372399205</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0.49424926622948601</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0.76213798887677797</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.37421148005173038</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.57140119960129465</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.72351136706077479</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.2417399589306776</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.98165168044452178</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.84316283238532219</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.99186880666392008</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.82627557802331231</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.59116415214474283</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.82190333776760016</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0.1545147463754622</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.65334894935990884</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.71628953632610959</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.20064837329793622</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.97947956197607022</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.86351000688016799</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.98320737442114547</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.80878747807646134</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.4911219056635982</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.89675692628468051</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0.29932832894666606</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.65347283491018859</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.76877797256873581</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.40267610210742577</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.97549414358397502</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.80661754862960211</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.99141605928747079</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.88420107414986993</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.57174341330365763</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.9157770543961139</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.26441297412459658</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.66634234027059758</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.64906382912370086</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.29793744252784621</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.95372894920761675</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.87840794610054229</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.97557728713671654</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.84576414657741306</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.50541194014126856</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0.85059266795067878</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.28702637311285661</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.66233393721511202</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.75341673947714261</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.36189467345289439</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.97735851906581939</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.85949728253482438</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.9889745410054388</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.90608499902474249</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.56060051104631581</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.8757095807787435</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0.34898905998549401</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.68469339504144799</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.78397341712063995</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.41415164550976702</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.98324036000270698</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.848412412405389</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0.99648985102443999</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.92555413562882605</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.58459706730166605</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0.92828689342139803</v>
+      </c>
+      <c r="L11">
+        <f>AVERAGE(B24:K24)</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <f>RANK(B2,B$2:B$11)</f>
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:K15" si="1">RANK(C2,C$2:C$11)</f>
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:K24" si="2">RANK(B3,B$2:B$11)</f>
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="9">
+        <f>MAX(B2:B11)</f>
+        <v>0.37421148005173038</v>
+      </c>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:L27" si="3">MAX(C2:C11)</f>
+        <v>0.68469339504144799</v>
+      </c>
+      <c r="D27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.78397341712063995</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.68257175690876104</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.98779364707108597</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.98373834829475304</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.99678790185553701</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.92555413562882605</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.59116415214474283</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="3"/>
+        <v>0.92828689342139803</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="3"/>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="6">
+        <f>LARGE(B2:B11,2)</f>
+        <v>0.34898905998549401</v>
+      </c>
+      <c r="C28" s="6">
+        <f t="shared" ref="C28:L28" si="4">LARGE(C2:C11,2)</f>
+        <v>0.67942171881000801</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.76877797256873581</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.62834450918373896</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.98324036000270698</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.87840794610054229</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.99648985102443999</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.90608499902474249</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.58459706730166605</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="4"/>
+        <v>0.9157770543961139</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="4"/>
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="45">
+      <c r="A30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="19" t="str">
+        <f>"\textbf{"&amp;TEXT(B27,"0.0000")&amp;"}"</f>
+        <v>\textbf{0.3742}</v>
+      </c>
+      <c r="C30" s="19" t="str">
+        <f t="shared" ref="C30:K30" si="5">"\textbf{"&amp;TEXT(C27,"0.0000")&amp;"}"</f>
+        <v>\textbf{0.6847}</v>
+      </c>
+      <c r="D30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.7840}</v>
+      </c>
+      <c r="E30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.6826}</v>
+      </c>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9878}</v>
+      </c>
+      <c r="G30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9837}</v>
+      </c>
+      <c r="H30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9968}</v>
+      </c>
+      <c r="I30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9256}</v>
+      </c>
+      <c r="J30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.5912}</v>
+      </c>
+      <c r="K30" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\textbf{0.9283}</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="45">
+      <c r="A31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="19" t="str">
+        <f>"\underline{"&amp;TEXT(B28,"0.0000")&amp;"}"</f>
+        <v>\underline{0.3490}</v>
+      </c>
+      <c r="C31" s="19" t="str">
+        <f t="shared" ref="C31:K31" si="6">"\underline{"&amp;TEXT(C28,"0.0000")&amp;"}"</f>
+        <v>\underline{0.6794}</v>
+      </c>
+      <c r="D31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.7688}</v>
+      </c>
+      <c r="E31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.6283}</v>
+      </c>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9832}</v>
+      </c>
+      <c r="G31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.8784}</v>
+      </c>
+      <c r="H31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9965}</v>
+      </c>
+      <c r="I31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9061}</v>
+      </c>
+      <c r="J31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.5846}</v>
+      </c>
+      <c r="K31" s="19" t="str">
+        <f t="shared" si="6"/>
+        <v>\underline{0.9158}</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDB590A-3AFB-AE47-9063-116F98C8643F}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15">
+      <c r="A1" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0.28060836501901099</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0.679341657207718</v>
+      </c>
+      <c r="D2" s="9">
+        <v>0.75024390243902395</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.67341176470588204</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0.98756756756756703</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0.804624277456647</v>
+      </c>
+      <c r="H2" s="9">
+        <v>0.99672578444747595</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0.823890784982935</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0.49888888888888899</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0.90375000000000005</v>
+      </c>
+      <c r="L2" s="22">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0.224334600760456</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.49920544835414299</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.67317073170731601</v>
+      </c>
+      <c r="E3" s="9">
+        <v>7.55294117647059E-2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.45189189189189199</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.98150289017340997</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0.25102319236016302</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0.70307167235494805</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0.55333333333333301</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0.72250000000000003</v>
+      </c>
+      <c r="L3" s="22">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="9">
+        <v>0.315589353612167</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.52866061293984101</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.65853658536585302</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.60705882352941098</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.95135135135135096</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.69364161849710904</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.96271032287403302</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.77474402730375402</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0.53888888888888797</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0.90312499999999996</v>
+      </c>
+      <c r="L4" s="22">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.27604562737642502</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.52866061293984101</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.74829268292682904</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.59058823529411697</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.98162162162162103</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.804624277456647</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0.987539790814006</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.82525597269624495</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0.49444444444444402</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0.75875000000000004</v>
+      </c>
+      <c r="L5" s="22">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.33916349809885898</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.57111237230419942</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.73853658536585298</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.2447058823529408</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.98108108108108083</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.83236994219653138</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.99172351068667519</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.81843003412969251</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.58666666666666623</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0.82187500000000002</v>
+      </c>
+      <c r="L6" s="22">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0.26235741444866878</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.65317820658342762</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.73170731707317005</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.2049411764705876</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.97891891891891836</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.85549132947976836</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.98290131878126386</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.75563139931740575</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.49111111111111061</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="L7" s="22">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0.283650190114068</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.65164585698070332</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.77756097560975579</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.40305882352941136</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.9745945945945943</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.76531791907514402</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.99126875852660257</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.87781569965870287</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.5699999999999994</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.91187499999999999</v>
+      </c>
+      <c r="L8" s="22">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.26311787072243298</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.66520998864926173</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.66048780487804826</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.26964705882352902</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.95189189189189138</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.85433526011560657</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.97517053206002691</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.83617747440273005</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.5055555555555552</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="L9" s="22">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.304942965779467</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.66061293984108915</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.76585365853658482</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.32658823529411701</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.97675675675675622</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.83930635838150247</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.98881309686220986</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.90443686006825907</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.86875000000000002</v>
+      </c>
+      <c r="L10" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0.31787072243345998</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.68269012485811498</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.79512195121951201</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.41835294117646998</v>
+      </c>
+      <c r="F11" s="7">
+        <v>0.98270270270270299</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.83583815028901698</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0.99645293315143202</v>
+      </c>
+      <c r="I11" s="7">
+        <v>0.92423208191126305</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0.91937500000000005</v>
+      </c>
+      <c r="L11" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="22"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <f>RANK(B2,B$2:B$11)</f>
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:K15" si="0">RANK(C2,C$2:C$11)</f>
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L15" s="22"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <f t="shared" ref="B16:K24" si="1">RANK(B3,B$2:B$11)</f>
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L17" s="22"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="L19" s="22"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L20" s="22"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L21" s="22"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="L22" s="22"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L24" s="22"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="L25" s="22"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="L26" s="22"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="9">
+        <f>MAX(B2:B11)</f>
+        <v>0.33916349809885898</v>
+      </c>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:K27" si="2">MAX(C2:C11)</f>
+        <v>0.68269012485811498</v>
+      </c>
+      <c r="D27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.79512195121951201</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.67341176470588204</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.98756756756756703</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.98150289017340997</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.99672578444747595</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.92423208191126305</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.58666666666666623</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="2"/>
+        <v>0.91937500000000005</v>
+      </c>
+      <c r="L27" s="23">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="6">
+        <f>LARGE(B2:B11,2)</f>
+        <v>0.31787072243345998</v>
+      </c>
+      <c r="C28" s="6">
+        <f t="shared" ref="C28:K28" si="3">LARGE(C2:C11,2)</f>
+        <v>0.679341657207718</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.77756097560975579</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.60705882352941098</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.98270270270270299</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.85549132947976836</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.99645293315143202</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.90443686006825907</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="3"/>
+        <v>0.91187499999999999</v>
+      </c>
+      <c r="L28" s="22">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="L29" s="22"/>
+    </row>
+    <row r="30" spans="1:12" ht="45">
+      <c r="A30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="19" t="str">
+        <f>"\textbf{"&amp;TEXT(B27,"0.0000")&amp;"}"</f>
+        <v>\textbf{0.3392}</v>
+      </c>
+      <c r="C30" s="19" t="str">
+        <f t="shared" ref="C30:K30" si="4">"\textbf{"&amp;TEXT(C27,"0.0000")&amp;"}"</f>
+        <v>\textbf{0.6827}</v>
+      </c>
+      <c r="D30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.7951}</v>
+      </c>
+      <c r="E30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.6734}</v>
+      </c>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.9876}</v>
+      </c>
+      <c r="G30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.9815}</v>
+      </c>
+      <c r="H30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.9967}</v>
+      </c>
+      <c r="I30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.9242}</v>
+      </c>
+      <c r="J30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.5867}</v>
+      </c>
+      <c r="K30" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>\textbf{0.9194}</v>
+      </c>
+      <c r="L30" s="22"/>
+    </row>
+    <row r="31" spans="1:12" ht="45">
+      <c r="A31" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="19" t="str">
+        <f>"\underline{"&amp;TEXT(B28,"0.0000")&amp;"}"</f>
+        <v>\underline{0.3179}</v>
+      </c>
+      <c r="C31" s="19" t="str">
+        <f t="shared" ref="C31:K31" si="5">"\underline{"&amp;TEXT(C28,"0.0000")&amp;"}"</f>
+        <v>\underline{0.6793}</v>
+      </c>
+      <c r="D31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.7776}</v>
+      </c>
+      <c r="E31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.6071}</v>
+      </c>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.9827}</v>
+      </c>
+      <c r="G31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.8555}</v>
+      </c>
+      <c r="H31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.9965}</v>
+      </c>
+      <c r="I31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.9044}</v>
+      </c>
+      <c r="J31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.5833}</v>
+      </c>
+      <c r="K31" s="19" t="str">
+        <f t="shared" si="5"/>
+        <v>\underline{0.9119}</v>
+      </c>
+      <c r="L31" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1367,7 +4243,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="17.6" spans="1:11">
+    <row r="2" spans="1:11" ht="16">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1402,7 +4278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="17.6" spans="1:11">
+    <row r="3" spans="1:11" ht="16">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -1410,22 +4286,22 @@
         <v>0.290735772272735</v>
       </c>
       <c r="C3" s="5">
-        <v>0.182418360556114</v>
+        <v>0.18241836055611399</v>
       </c>
       <c r="D3" s="5">
-        <v>0.370086479711832</v>
+        <v>0.37008647971183201</v>
       </c>
       <c r="E3" s="5">
         <v>0.234435352803713</v>
       </c>
       <c r="F3" s="5">
-        <v>0.307965440842113</v>
+        <v>0.30796544084211303</v>
       </c>
       <c r="G3" s="5">
-        <v>0.349180938866396</v>
+        <v>0.34918093886639601</v>
       </c>
       <c r="H3" s="6">
-        <v>0.257418475559312</v>
+        <v>0.25741847555931202</v>
       </c>
       <c r="I3" s="6">
         <v>0.220976587842457</v>
@@ -1434,92 +4310,92 @@
         <v>0.255437385124617</v>
       </c>
       <c r="K3" s="7">
-        <v>0.3062</v>
-      </c>
-    </row>
-    <row r="4" ht="17.6" spans="1:11">
+        <v>0.30620000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="5">
-        <v>0.570675008929852</v>
+        <v>0.57067500892985201</v>
       </c>
       <c r="C4" s="5">
-        <v>0.653086909710686</v>
+        <v>0.65308690971068595</v>
       </c>
       <c r="D4" s="5">
-        <v>0.59981564263385</v>
+        <v>0.59981564263385001</v>
       </c>
       <c r="E4" s="5">
-        <v>0.499399306457916</v>
+        <v>0.49939930645791603</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5">
-        <v>0.527331297666993</v>
+        <v>0.52733129766699305</v>
       </c>
       <c r="H4" s="6">
-        <v>0.650625395905054</v>
+        <v>0.65062539590505397</v>
       </c>
       <c r="I4" s="6">
-        <v>0.664623623838512</v>
+        <v>0.66462362383851203</v>
       </c>
       <c r="J4" s="6">
-        <v>0.659724675544702</v>
+        <v>0.65972467554470204</v>
       </c>
       <c r="K4" s="7">
-        <v>0.6819</v>
-      </c>
-    </row>
-    <row r="5" ht="17.6" spans="1:11">
+        <v>0.68189999999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5">
-        <v>0.724938912889254</v>
+        <v>0.72493891288925405</v>
       </c>
       <c r="C5" s="5">
-        <v>0.721355429129395</v>
+        <v>0.72135542912939499</v>
       </c>
       <c r="D5" s="5">
-        <v>0.665860893743947</v>
+        <v>0.66586089374394697</v>
       </c>
       <c r="E5" s="5">
-        <v>0.688343202802219</v>
+        <v>0.68834320280221895</v>
       </c>
       <c r="F5" s="5">
         <v>0.629452788848895</v>
       </c>
       <c r="G5" s="5">
-        <v>0.641042797796122</v>
+        <v>0.64104279779612205</v>
       </c>
       <c r="H5" s="6">
-        <v>0.7709838526833</v>
+        <v>0.77098385268330005</v>
       </c>
       <c r="I5" s="6">
-        <v>0.653499383288176</v>
+        <v>0.65349938328817603</v>
       </c>
       <c r="J5" s="6">
-        <v>0.732783968310113</v>
+        <v>0.73278396831011305</v>
       </c>
       <c r="K5" s="7">
-        <v>0.7818</v>
-      </c>
-    </row>
-    <row r="6" ht="17.6" spans="1:11">
+        <v>0.78180000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5">
-        <v>0.21154719374797</v>
+        <v>0.21154719374797001</v>
       </c>
       <c r="C6" s="5">
         <v>0.174866885983225</v>
       </c>
       <c r="D6" s="5">
-        <v>0.243958545264983</v>
+        <v>0.24395854526498301</v>
       </c>
       <c r="E6" s="5">
-        <v>0.0957377459969095</v>
+        <v>9.5737745996909498E-2</v>
       </c>
       <c r="F6" s="5">
         <v>0.313460607250237</v>
@@ -1528,220 +4404,220 @@
         <v>0.246465993179869</v>
       </c>
       <c r="H6" s="6">
-        <v>0.37103606819473</v>
+        <v>0.37103606819473001</v>
       </c>
       <c r="I6" s="6">
         <v>0.255416230053439</v>
       </c>
       <c r="J6" s="6">
-        <v>0.304138216197549</v>
+        <v>0.30413821619754899</v>
       </c>
       <c r="K6" s="7">
         <v>0.3957</v>
       </c>
     </row>
-    <row r="7" ht="17.6" spans="1:11">
+    <row r="7" spans="1:11" ht="16">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="5">
-        <v>0.981083787599641</v>
+        <v>0.98108378759964099</v>
       </c>
       <c r="C7" s="5">
-        <v>0.978936292264671</v>
+        <v>0.97893629226467105</v>
       </c>
       <c r="D7" s="5">
-        <v>0.98013352740756</v>
+        <v>0.98013352740755999</v>
       </c>
       <c r="E7" s="5">
-        <v>0.70193564643135</v>
+        <v>0.70193564643134998</v>
       </c>
       <c r="F7" s="5">
-        <v>0.910767241490622</v>
+        <v>0.91076724149062205</v>
       </c>
       <c r="G7" s="5">
-        <v>0.981264144879912</v>
+        <v>0.98126414487991198</v>
       </c>
       <c r="H7" s="6">
-        <v>0.974727202068643</v>
+        <v>0.97472720206864305</v>
       </c>
       <c r="I7" s="6">
         <v>0.952219721923519</v>
       </c>
       <c r="J7" s="6">
-        <v>0.976771336047927</v>
+        <v>0.97677133604792699</v>
       </c>
       <c r="K7" s="7">
-        <v>0.9828</v>
-      </c>
-    </row>
-    <row r="8" ht="17.6" spans="1:11">
+        <v>0.98280000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="5">
-        <v>0.828650847528709</v>
+        <v>0.82865084752870899</v>
       </c>
       <c r="C8" s="5">
-        <v>0.854546536267009</v>
+        <v>0.85454653626700905</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>0.769107875961365</v>
+        <v>0.76910787596136498</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="6">
-        <v>0.765967703865324</v>
+        <v>0.76596770386532398</v>
       </c>
       <c r="I8" s="6">
-        <v>0.856022254150792</v>
+        <v>0.85602225415079203</v>
       </c>
       <c r="J8" s="6">
-        <v>0.839170725489192</v>
+        <v>0.83917072548919203</v>
       </c>
       <c r="K8" s="7">
-        <v>0.8362</v>
-      </c>
-    </row>
-    <row r="9" ht="17.6" spans="1:11">
+        <v>0.83620000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="5">
-        <v>0.991726658199298</v>
+        <v>0.99172665819929795</v>
       </c>
       <c r="C9" s="5">
-        <v>0.98287272906509</v>
+        <v>0.98287272906509004</v>
       </c>
       <c r="D9" s="5">
-        <v>0.990713701430398</v>
+        <v>0.99071370143039805</v>
       </c>
       <c r="E9" s="5">
-        <v>0.529809042080487</v>
+        <v>0.52980904208048696</v>
       </c>
       <c r="F9" s="5">
-        <v>0.97325570132208</v>
+        <v>0.97325570132207995</v>
       </c>
       <c r="G9" s="5">
-        <v>0.987172665212886</v>
+        <v>0.98717266521288605</v>
       </c>
       <c r="H9" s="6">
-        <v>0.991275031558086</v>
+        <v>0.99127503155808605</v>
       </c>
       <c r="I9" s="6">
-        <v>0.975168941327908</v>
+        <v>0.97516894132790799</v>
       </c>
       <c r="J9" s="6">
-        <v>0.988797238398018</v>
+        <v>0.98879723839801803</v>
       </c>
       <c r="K9" s="7">
-        <v>0.9965</v>
-      </c>
-    </row>
-    <row r="10" ht="17.6" spans="1:11">
+        <v>0.99650000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="5">
-        <v>0.817402011215574</v>
+        <v>0.81740201121557399</v>
       </c>
       <c r="C10" s="5">
-        <v>0.744080639681733</v>
+        <v>0.74408063968173299</v>
       </c>
       <c r="D10" s="5">
-        <v>0.881822010694043</v>
+        <v>0.88182201069404298</v>
       </c>
       <c r="E10" s="5">
-        <v>0.542893480160721</v>
+        <v>0.54289348016072103</v>
       </c>
       <c r="F10" s="5">
-        <v>0.771911563059862</v>
+        <v>0.77191156305986197</v>
       </c>
       <c r="G10" s="5">
-        <v>0.895524533694484</v>
+        <v>0.89552453369448404</v>
       </c>
       <c r="H10" s="6">
-        <v>0.877249359124821</v>
+        <v>0.87724935912482105</v>
       </c>
       <c r="I10" s="6">
-        <v>0.834876246878077</v>
+        <v>0.83487624687807704</v>
       </c>
       <c r="J10" s="6">
-        <v>0.904335760974732</v>
+        <v>0.90433576097473201</v>
       </c>
       <c r="K10" s="7">
-        <v>0.9242</v>
-      </c>
-    </row>
-    <row r="11" ht="17.6" spans="1:11">
+        <v>0.92420000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="5">
-        <v>0.580967510106739</v>
+        <v>0.58096751010673897</v>
       </c>
       <c r="C11" s="5">
-        <v>0.488957077162016</v>
+        <v>0.48895707716201597</v>
       </c>
       <c r="D11" s="5">
-        <v>0.486796514491976</v>
+        <v>0.48679651449197597</v>
       </c>
       <c r="E11" s="5">
         <v>0.453104706785391</v>
       </c>
       <c r="F11" s="5">
-        <v>0.487306501547987</v>
+        <v>0.48730650154798699</v>
       </c>
       <c r="G11" s="5">
-        <v>0.478603027154302</v>
+        <v>0.47860302715430197</v>
       </c>
       <c r="H11" s="6">
-        <v>0.567565981319303</v>
+        <v>0.56756598131930303</v>
       </c>
       <c r="I11" s="6">
-        <v>0.503831869962687</v>
+        <v>0.50383186996268703</v>
       </c>
       <c r="J11" s="6">
-        <v>0.547859467098639</v>
+        <v>0.54785946709863897</v>
       </c>
       <c r="K11" s="7">
-        <v>0.5818</v>
-      </c>
-    </row>
-    <row r="12" ht="17.6" spans="1:11">
+        <v>0.58179999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="5">
-        <v>0.81885013476078</v>
+        <v>0.81885013476077995</v>
       </c>
       <c r="C12" s="5">
-        <v>0.889326886840967</v>
+        <v>0.88932688684096695</v>
       </c>
       <c r="D12" s="5">
-        <v>0.867983406428908</v>
+        <v>0.86798340642890803</v>
       </c>
       <c r="E12" s="5">
-        <v>0.409991450914013</v>
+        <v>0.40999145091401301</v>
       </c>
       <c r="F12" s="5">
-        <v>0.856082543873074</v>
+        <v>0.85608254387307403</v>
       </c>
       <c r="G12" s="5">
-        <v>0.864146138827166</v>
+        <v>0.86414613882716595</v>
       </c>
       <c r="H12" s="6">
-        <v>0.911430193607551</v>
+        <v>0.91143019360755095</v>
       </c>
       <c r="I12" s="6">
-        <v>0.843872811909272</v>
+        <v>0.84387281190927199</v>
       </c>
       <c r="J12" s="6">
-        <v>0.869009559149049</v>
+        <v>0.86900955914904898</v>
       </c>
       <c r="K12" s="7">
-        <v>0.9193</v>
+        <v>0.91930000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1782,7 +4658,7 @@
       </c>
       <c r="J13" s="6">
         <f t="shared" si="0"/>
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="K13" s="6">
         <f t="shared" si="0"/>
@@ -1800,7 +4676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="17.6" spans="1:11">
+    <row r="17" spans="1:11" ht="16">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -1845,7 +4721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="17.6" spans="1:11">
+    <row r="18" spans="1:11" ht="16">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -1890,7 +4766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="17.6" spans="1:11">
+    <row r="19" spans="1:11" ht="16">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -1935,7 +4811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="17.6" spans="1:11">
+    <row r="20" spans="1:11" ht="16">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
@@ -1980,7 +4856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17.6" spans="1:11">
+    <row r="21" spans="1:11" ht="16">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
@@ -2025,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="17.6" spans="1:11">
+    <row r="22" spans="1:11" ht="16">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -2070,7 +4946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="17.6" spans="1:11">
+    <row r="23" spans="1:11" ht="16">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
@@ -2115,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="17.6" spans="1:11">
+    <row r="24" spans="1:11" ht="16">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
@@ -2160,7 +5036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17.6" spans="1:11">
+    <row r="25" spans="1:11" ht="16">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
@@ -2205,7 +5081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="17.6" spans="1:11">
+    <row r="26" spans="1:11" ht="16">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
@@ -2251,30 +5127,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.6923076923077" customWidth="1"/>
-    <col min="2" max="2" width="14.3076923076923" customWidth="1"/>
-    <col min="3" max="3" width="12.6153846153846" customWidth="1"/>
-    <col min="4" max="4" width="15.0769230769231" customWidth="1"/>
-    <col min="5" max="5" width="14.6923076923077" customWidth="1"/>
-    <col min="6" max="6" width="23.1538461538462" customWidth="1"/>
-    <col min="7" max="7" width="8.69230769230769" customWidth="1"/>
-    <col min="8" max="8" width="10.9230769230769" customWidth="1"/>
-    <col min="9" max="9" width="10.4615384615385" customWidth="1"/>
-    <col min="10" max="10" width="10.3846153846154" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:11">
+    <row r="1" spans="1:11" ht="16">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -2285,7 +5160,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="17.6" spans="1:11">
+    <row r="2" spans="1:11" ht="16">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2320,145 +5195,145 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="17.6" spans="1:11">
+    <row r="3" spans="1:11" ht="16">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="5">
-        <v>0.37421148005173</v>
+        <v>0.37421148005172999</v>
       </c>
       <c r="C3" s="5">
         <v>0.154514746375462</v>
       </c>
       <c r="D3" s="5">
-        <v>0.374667715008251</v>
+        <v>0.37466771500825102</v>
       </c>
       <c r="E3" s="5">
-        <v>0.239341620108538</v>
+        <v>0.23934162010853799</v>
       </c>
       <c r="F3" s="5">
         <v>0.30996835863756</v>
       </c>
       <c r="G3" s="5">
-        <v>0.390426488342306</v>
+        <v>0.39042648834230598</v>
       </c>
       <c r="H3" s="6">
         <v>0.299328328946666</v>
       </c>
       <c r="I3" s="6">
-        <v>0.264412974124597</v>
+        <v>0.26441297412459702</v>
       </c>
       <c r="J3" s="6">
         <v>0.287026373112857</v>
       </c>
       <c r="K3" s="7">
-        <v>0.349</v>
-      </c>
-    </row>
-    <row r="4" ht="17.6" spans="1:11">
+        <v>0.34899999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="5">
-        <v>0.571401199601295</v>
+        <v>0.57140119960129498</v>
       </c>
       <c r="C4" s="5">
-        <v>0.653348949359909</v>
+        <v>0.65334894935990895</v>
       </c>
       <c r="D4" s="5">
-        <v>0.600073722950855</v>
+        <v>0.60007372295085504</v>
       </c>
       <c r="E4" s="5">
-        <v>0.499432106237985</v>
+        <v>0.49943210623798501</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5">
-        <v>0.547609211346485</v>
+        <v>0.54760921134648499</v>
       </c>
       <c r="H4" s="6">
-        <v>0.653472834910189</v>
+        <v>0.65347283491018904</v>
       </c>
       <c r="I4" s="6">
-        <v>0.666342340270598</v>
+        <v>0.66634234027059802</v>
       </c>
       <c r="J4" s="6">
-        <v>0.662333937215112</v>
+        <v>0.66233393721511202</v>
       </c>
       <c r="K4" s="7">
-        <v>0.6847</v>
-      </c>
-    </row>
-    <row r="5" ht="17.6" spans="1:11">
+        <v>0.68469999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5">
-        <v>0.723511367060775</v>
+        <v>0.72351136706077501</v>
       </c>
       <c r="C5" s="5">
-        <v>0.71628953632611</v>
+        <v>0.71628953632611003</v>
       </c>
       <c r="D5" s="5">
-        <v>0.664687403173971</v>
+        <v>0.66468740317397101</v>
       </c>
       <c r="E5" s="5">
-        <v>0.680729676685008</v>
+        <v>0.68072967668500795</v>
       </c>
       <c r="F5" s="5">
-        <v>0.613166854470333</v>
+        <v>0.61316685447033303</v>
       </c>
       <c r="G5" s="5">
-        <v>0.638061492756417</v>
+        <v>0.63806149275641699</v>
       </c>
       <c r="H5" s="6">
-        <v>0.768777972568736</v>
+        <v>0.76877797256873603</v>
       </c>
       <c r="I5" s="6">
-        <v>0.649063829123701</v>
+        <v>0.64906382912370097</v>
       </c>
       <c r="J5" s="6">
-        <v>0.753416739477143</v>
+        <v>0.75341673947714305</v>
       </c>
       <c r="K5" s="7">
-        <v>0.784</v>
-      </c>
-    </row>
-    <row r="6" ht="17.6" spans="1:11">
+        <v>0.78400000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5">
-        <v>0.241739958930678</v>
+        <v>0.24173995893067801</v>
       </c>
       <c r="C6" s="5">
         <v>0.200648373297936</v>
       </c>
       <c r="D6" s="5">
-        <v>0.316103798529954</v>
+        <v>0.31610379852995402</v>
       </c>
       <c r="E6" s="5">
         <v>0.106804708817083</v>
       </c>
       <c r="F6" s="5">
-        <v>0.345403459049468</v>
+        <v>0.34540345904946801</v>
       </c>
       <c r="G6" s="5">
-        <v>0.281887510133942</v>
+        <v>0.28188751013394198</v>
       </c>
       <c r="H6" s="6">
-        <v>0.402676102107426</v>
+        <v>0.40267610210742599</v>
       </c>
       <c r="I6" s="6">
-        <v>0.297937442527846</v>
+        <v>0.29793744252784599</v>
       </c>
       <c r="J6" s="6">
         <v>0.361894673452894</v>
       </c>
       <c r="K6" s="7">
-        <v>0.4142</v>
-      </c>
-    </row>
-    <row r="7" ht="17.6" spans="1:11">
+        <v>0.41420000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -2472,40 +5347,40 @@
         <v>0.980639340632666</v>
       </c>
       <c r="E7" s="5">
-        <v>0.735800150945238</v>
+        <v>0.73580015094523799</v>
       </c>
       <c r="F7" s="5">
-        <v>0.91383000405581</v>
+        <v>0.91383000405581005</v>
       </c>
       <c r="G7" s="5">
-        <v>0.982004572451575</v>
+        <v>0.98200457245157502</v>
       </c>
       <c r="H7" s="6">
-        <v>0.975494143583975</v>
+        <v>0.97549414358397502</v>
       </c>
       <c r="I7" s="6">
-        <v>0.953728949207617</v>
+        <v>0.95372894920761697</v>
       </c>
       <c r="J7" s="6">
-        <v>0.977358519065819</v>
+        <v>0.97735851906581905</v>
       </c>
       <c r="K7" s="7">
-        <v>0.9832</v>
-      </c>
-    </row>
-    <row r="8" ht="17.6" spans="1:11">
+        <v>0.98319999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="5">
-        <v>0.843162832385322</v>
+        <v>0.84316283238532197</v>
       </c>
       <c r="C8" s="5">
-        <v>0.863510006880168</v>
+        <v>0.86351000688016799</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>0.780008499405037</v>
+        <v>0.78000849940503703</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -2513,153 +5388,153 @@
         <v>0.806617548629602</v>
       </c>
       <c r="I8" s="6">
-        <v>0.878407946100542</v>
+        <v>0.87840794610054196</v>
       </c>
       <c r="J8" s="6">
-        <v>0.859497282534824</v>
+        <v>0.85949728253482405</v>
       </c>
       <c r="K8" s="7">
-        <v>0.8484</v>
-      </c>
-    </row>
-    <row r="9" ht="17.6" spans="1:11">
+        <v>0.84840000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="5">
-        <v>0.99186880666392</v>
+        <v>0.99186880666391997</v>
       </c>
       <c r="C9" s="5">
-        <v>0.983207374421145</v>
+        <v>0.98320737442114503</v>
       </c>
       <c r="D9" s="5">
-        <v>0.990808440823912</v>
+        <v>0.99080844082391195</v>
       </c>
       <c r="E9" s="5">
-        <v>0.552054940754641</v>
+        <v>0.55205494075464101</v>
       </c>
       <c r="F9" s="5">
-        <v>0.97372082614304</v>
+        <v>0.97372082614304001</v>
       </c>
       <c r="G9" s="5">
-        <v>0.987367312715221</v>
+        <v>0.98736731271522105</v>
       </c>
       <c r="H9" s="6">
-        <v>0.991416059287471</v>
+        <v>0.99141605928747101</v>
       </c>
       <c r="I9" s="6">
-        <v>0.975577287136717</v>
+        <v>0.97557728713671699</v>
       </c>
       <c r="J9" s="6">
-        <v>0.988974541005439</v>
+        <v>0.98897454100543902</v>
       </c>
       <c r="K9" s="7">
-        <v>0.9965</v>
-      </c>
-    </row>
-    <row r="10" ht="17.6" spans="1:11">
+        <v>0.99650000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="5">
-        <v>0.826275578023312</v>
+        <v>0.82627557802331197</v>
       </c>
       <c r="C10" s="5">
-        <v>0.808787478076461</v>
+        <v>0.80878747807646101</v>
       </c>
       <c r="D10" s="5">
-        <v>0.883173440119757</v>
+        <v>0.88317344011975696</v>
       </c>
       <c r="E10" s="5">
-        <v>0.702604136094752</v>
+        <v>0.70260413609475203</v>
       </c>
       <c r="F10" s="5">
-        <v>0.813389341034392</v>
+        <v>0.81338934103439198</v>
       </c>
       <c r="G10" s="5">
-        <v>0.896085024324364</v>
+        <v>0.89608502432436399</v>
       </c>
       <c r="H10" s="6">
-        <v>0.88420107414987</v>
+        <v>0.88420107414987004</v>
       </c>
       <c r="I10" s="6">
-        <v>0.845764146577413</v>
+        <v>0.84576414657741295</v>
       </c>
       <c r="J10" s="6">
-        <v>0.906084999024742</v>
+        <v>0.90608499902474204</v>
       </c>
       <c r="K10" s="7">
-        <v>0.9256</v>
-      </c>
-    </row>
-    <row r="11" ht="17.6" spans="1:11">
+        <v>0.92559999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="5">
-        <v>0.591164152144743</v>
+        <v>0.59116415214474305</v>
       </c>
       <c r="C11" s="5">
-        <v>0.491121905663598</v>
+        <v>0.49112190566359798</v>
       </c>
       <c r="D11" s="5">
-        <v>0.487607610320658</v>
+        <v>0.48760761032065802</v>
       </c>
       <c r="E11" s="5">
-        <v>0.47504771304698</v>
+        <v>0.47504771304698001</v>
       </c>
       <c r="F11" s="5">
-        <v>0.488749999999999</v>
+        <v>0.48874999999999902</v>
       </c>
       <c r="G11" s="5">
-        <v>0.478845663761775</v>
+        <v>0.47884566376177501</v>
       </c>
       <c r="H11" s="6">
-        <v>0.571743413303658</v>
+        <v>0.57174341330365797</v>
       </c>
       <c r="I11" s="6">
         <v>0.505411940141269</v>
       </c>
       <c r="J11" s="6">
-        <v>0.560600511046316</v>
+        <v>0.56060051104631603</v>
       </c>
       <c r="K11" s="7">
-        <v>0.5846</v>
-      </c>
-    </row>
-    <row r="12" ht="17.6" spans="1:11">
+        <v>0.58460000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="5">
-        <v>0.8219033377676</v>
+        <v>0.82190333776760005</v>
       </c>
       <c r="C12" s="5">
-        <v>0.896756926284681</v>
+        <v>0.89675692628468096</v>
       </c>
       <c r="D12" s="5">
-        <v>0.878519020639314</v>
+        <v>0.87851902063931397</v>
       </c>
       <c r="E12" s="5">
-        <v>0.425814987034062</v>
+        <v>0.42581498703406201</v>
       </c>
       <c r="F12" s="5">
-        <v>0.868016035058911</v>
+        <v>0.86801603505891101</v>
       </c>
       <c r="G12" s="5">
-        <v>0.875718675212127</v>
+        <v>0.87571867521212698</v>
       </c>
       <c r="H12" s="6">
-        <v>0.915777054396114</v>
+        <v>0.91577705439611401</v>
       </c>
       <c r="I12" s="6">
         <v>0.850592667950679</v>
       </c>
       <c r="J12" s="6">
-        <v>0.875709580778744</v>
+        <v>0.87570958077874395</v>
       </c>
       <c r="K12" s="7">
-        <v>0.9283</v>
+        <v>0.92830000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2668,7 +5543,7 @@
       </c>
       <c r="B13" s="6">
         <f t="shared" ref="B13:K13" si="0">SUM(B17:B26)/10</f>
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C13" s="6">
         <f t="shared" si="0"/>
@@ -2718,7 +5593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="17.6" spans="1:11">
+    <row r="17" spans="1:11" ht="16">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -2763,7 +5638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="17.6" spans="1:11">
+    <row r="18" spans="1:11" ht="16">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -2808,7 +5683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="17.6" spans="1:11">
+    <row r="19" spans="1:11" ht="16">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -2853,7 +5728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="17.6" spans="1:11">
+    <row r="20" spans="1:11" ht="16">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
@@ -2898,7 +5773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17.6" spans="1:11">
+    <row r="21" spans="1:11" ht="16">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
@@ -2943,7 +5818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="17.6" spans="1:11">
+    <row r="22" spans="1:11" ht="16">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -2988,7 +5863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="17.6" spans="1:11">
+    <row r="23" spans="1:11" ht="16">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
@@ -3033,7 +5908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="17.6" spans="1:11">
+    <row r="24" spans="1:11" ht="16">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
@@ -3078,7 +5953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17.6" spans="1:11">
+    <row r="25" spans="1:11" ht="16">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
@@ -3123,7 +5998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="17.6" spans="1:11">
+    <row r="26" spans="1:11" ht="16">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
@@ -3169,30 +6044,29 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.6923076923077" customWidth="1"/>
-    <col min="2" max="2" width="14.3076923076923" customWidth="1"/>
-    <col min="3" max="3" width="12.6153846153846" customWidth="1"/>
-    <col min="4" max="4" width="15.0769230769231" customWidth="1"/>
-    <col min="5" max="5" width="14.6923076923077" customWidth="1"/>
-    <col min="6" max="6" width="23.1538461538462" customWidth="1"/>
-    <col min="7" max="7" width="8.69230769230769" customWidth="1"/>
-    <col min="8" max="8" width="10.9230769230769" customWidth="1"/>
-    <col min="9" max="9" width="10.4615384615385" customWidth="1"/>
-    <col min="10" max="10" width="10.3846153846154" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:11">
+    <row r="1" spans="1:11" ht="16">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -3203,7 +6077,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="17.6" spans="1:11">
+    <row r="2" spans="1:11" ht="16">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -3238,110 +6112,110 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="17.6" spans="1:11">
+    <row r="3" spans="1:11" ht="16">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="5">
-        <v>0.339163498098859</v>
+        <v>0.33916349809885898</v>
       </c>
       <c r="C3" s="5">
         <v>0.262357414448669</v>
       </c>
       <c r="D3" s="5">
-        <v>0.374904942965779</v>
+        <v>0.37490494296577898</v>
       </c>
       <c r="E3" s="5">
-        <v>0.237262357414448</v>
+        <v>0.23726235741444801</v>
       </c>
       <c r="F3" s="5">
-        <v>0.307984790874524</v>
+        <v>0.30798479087452402</v>
       </c>
       <c r="G3" s="5">
-        <v>0.371102661596958</v>
+        <v>0.37110266159695798</v>
       </c>
       <c r="H3" s="6">
         <v>0.283650190114068</v>
       </c>
       <c r="I3" s="6">
-        <v>0.263117870722433</v>
+        <v>0.26311787072243298</v>
       </c>
       <c r="J3" s="6">
         <v>0.304942965779467</v>
       </c>
       <c r="K3" s="7">
-        <v>0.3179</v>
-      </c>
-    </row>
-    <row r="4" ht="17.6" spans="1:11">
+        <v>0.31790000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="16">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="5">
-        <v>0.571112372304199</v>
+        <v>0.57111237230419898</v>
       </c>
       <c r="C4" s="5">
-        <v>0.653178206583428</v>
+        <v>0.65317820658342796</v>
       </c>
       <c r="D4" s="5">
-        <v>0.59994324631101</v>
+        <v>0.59994324631101004</v>
       </c>
       <c r="E4" s="5">
-        <v>0.499432463110102</v>
+        <v>0.49943246311010198</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5">
-        <v>0.542111237230419</v>
+        <v>0.54211123723041899</v>
       </c>
       <c r="H4" s="6">
-        <v>0.651645856980703</v>
+        <v>0.65164585698070299</v>
       </c>
       <c r="I4" s="6">
-        <v>0.665209988649262</v>
+        <v>0.66520998864926195</v>
       </c>
       <c r="J4" s="6">
-        <v>0.660612939841089</v>
+        <v>0.66061293984108904</v>
       </c>
       <c r="K4" s="7">
-        <v>0.6827</v>
-      </c>
-    </row>
-    <row r="5" ht="17.6" spans="1:11">
+        <v>0.68269999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5">
-        <v>0.738536585365853</v>
+        <v>0.73853658536585298</v>
       </c>
       <c r="C5" s="5">
-        <v>0.73170731707317</v>
+        <v>0.73170731707317005</v>
       </c>
       <c r="D5" s="5">
-        <v>0.667317073170731</v>
+        <v>0.66731707317073097</v>
       </c>
       <c r="E5" s="5">
-        <v>0.704390243902438</v>
+        <v>0.70439024390243798</v>
       </c>
       <c r="F5" s="5">
-        <v>0.682926829268292</v>
+        <v>0.68292682926829196</v>
       </c>
       <c r="G5" s="5">
-        <v>0.644878048780487</v>
+        <v>0.64487804878048705</v>
       </c>
       <c r="H5" s="6">
-        <v>0.777560975609756</v>
+        <v>0.77756097560975601</v>
       </c>
       <c r="I5" s="6">
-        <v>0.660487804878048</v>
+        <v>0.66048780487804803</v>
       </c>
       <c r="J5" s="6">
-        <v>0.765853658536585</v>
+        <v>0.76585365853658505</v>
       </c>
       <c r="K5" s="7">
-        <v>0.7951</v>
-      </c>
-    </row>
-    <row r="6" ht="17.6" spans="1:11">
+        <v>0.79510000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="16">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -3349,168 +6223,168 @@
         <v>0.244705882352941</v>
       </c>
       <c r="C6" s="5">
-        <v>0.204941176470588</v>
+        <v>0.20494117647058799</v>
       </c>
       <c r="D6" s="5">
-        <v>0.273176470588235</v>
+        <v>0.27317647058823502</v>
       </c>
       <c r="E6" s="5">
-        <v>0.0969411764705882</v>
+        <v>9.6941176470588197E-2</v>
       </c>
       <c r="F6" s="5">
-        <v>0.331764705882352</v>
+        <v>0.33176470588235202</v>
       </c>
       <c r="G6" s="5">
         <v>0.26</v>
       </c>
       <c r="H6" s="6">
-        <v>0.403058823529411</v>
+        <v>0.40305882352941103</v>
       </c>
       <c r="I6" s="6">
-        <v>0.269647058823529</v>
+        <v>0.26964705882352902</v>
       </c>
       <c r="J6" s="6">
-        <v>0.326588235294117</v>
+        <v>0.32658823529411701</v>
       </c>
       <c r="K6" s="7">
-        <v>0.4184</v>
-      </c>
-    </row>
-    <row r="7" ht="17.6" spans="1:11">
+        <v>0.41839999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="5">
-        <v>0.981081081081081</v>
+        <v>0.98108108108108105</v>
       </c>
       <c r="C7" s="5">
-        <v>0.978918918918918</v>
+        <v>0.97891891891891802</v>
       </c>
       <c r="D7" s="5">
         <v>0.98</v>
       </c>
       <c r="E7" s="5">
-        <v>0.695675675675675</v>
+        <v>0.69567567567567501</v>
       </c>
       <c r="F7" s="5">
-        <v>0.91081081081081</v>
+        <v>0.91081081081080995</v>
       </c>
       <c r="G7" s="5">
-        <v>0.981081081081081</v>
+        <v>0.98108108108108105</v>
       </c>
       <c r="H7" s="6">
-        <v>0.974594594594594</v>
+        <v>0.97459459459459397</v>
       </c>
       <c r="I7" s="6">
-        <v>0.951891891891891</v>
+        <v>0.95189189189189105</v>
       </c>
       <c r="J7" s="6">
-        <v>0.976756756756756</v>
+        <v>0.97675675675675599</v>
       </c>
       <c r="K7" s="7">
-        <v>0.9827</v>
-      </c>
-    </row>
-    <row r="8" ht="17.6" spans="1:11">
+        <v>0.98270000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="5">
-        <v>0.832369942196531</v>
+        <v>0.83236994219653104</v>
       </c>
       <c r="C8" s="5">
-        <v>0.855491329479768</v>
+        <v>0.85549132947976803</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>0.767630057803468</v>
+        <v>0.76763005780346805</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="6">
-        <v>0.765317919075144</v>
+        <v>0.76531791907514402</v>
       </c>
       <c r="I8" s="6">
-        <v>0.854335260115607</v>
+        <v>0.85433526011560701</v>
       </c>
       <c r="J8" s="6">
-        <v>0.839306358381502</v>
+        <v>0.83930635838150203</v>
       </c>
       <c r="K8" s="7">
-        <v>0.8358</v>
-      </c>
-    </row>
-    <row r="9" ht="17.6" spans="1:11">
+        <v>0.83579999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="5">
-        <v>0.991723510686675</v>
+        <v>0.99172351068667497</v>
       </c>
       <c r="C9" s="5">
-        <v>0.982901318781264</v>
+        <v>0.98290131878126397</v>
       </c>
       <c r="D9" s="5">
-        <v>0.990723055934515</v>
+        <v>0.99072305593451504</v>
       </c>
       <c r="E9" s="5">
-        <v>0.532060027285129</v>
+        <v>0.53206002728512902</v>
       </c>
       <c r="F9" s="5">
-        <v>0.973169622555707</v>
+        <v>0.97316962255570705</v>
       </c>
       <c r="G9" s="5">
-        <v>0.987175989085948</v>
+        <v>0.98717598908594795</v>
       </c>
       <c r="H9" s="6">
-        <v>0.991268758526603</v>
+        <v>0.99126875852660301</v>
       </c>
       <c r="I9" s="6">
-        <v>0.975170532060027</v>
+        <v>0.97517053206002702</v>
       </c>
       <c r="J9" s="6">
-        <v>0.98881309686221</v>
+        <v>0.98881309686220997</v>
       </c>
       <c r="K9" s="7">
-        <v>0.9965</v>
-      </c>
-    </row>
-    <row r="10" ht="17.6" spans="1:11">
+        <v>0.99650000000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="16">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="5">
-        <v>0.818430034129693</v>
+        <v>0.81843003412969295</v>
       </c>
       <c r="C10" s="5">
-        <v>0.755631399317406</v>
+        <v>0.75563139931740597</v>
       </c>
       <c r="D10" s="5">
-        <v>0.881911262798634</v>
+        <v>0.88191126279863397</v>
       </c>
       <c r="E10" s="5">
-        <v>0.599999999999999</v>
+        <v>0.59999999999999898</v>
       </c>
       <c r="F10" s="5">
-        <v>0.77815699658703</v>
+        <v>0.77815699658702997</v>
       </c>
       <c r="G10" s="5">
-        <v>0.89556313993174</v>
+        <v>0.89556313993173997</v>
       </c>
       <c r="H10" s="6">
-        <v>0.877815699658703</v>
+        <v>0.87781569965870299</v>
       </c>
       <c r="I10" s="6">
-        <v>0.83617747440273</v>
+        <v>0.83617747440273005</v>
       </c>
       <c r="J10" s="6">
-        <v>0.904436860068259</v>
+        <v>0.90443686006825896</v>
       </c>
       <c r="K10" s="7">
-        <v>0.9242</v>
-      </c>
-    </row>
-    <row r="11" ht="17.6" spans="1:11">
+        <v>0.92420000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="16">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -3521,60 +6395,60 @@
         <v>0.491111111111111</v>
       </c>
       <c r="D11" s="5">
-        <v>0.487777777777777</v>
+        <v>0.48777777777777698</v>
       </c>
       <c r="E11" s="5">
-        <v>0.478888888888888</v>
+        <v>0.47888888888888798</v>
       </c>
       <c r="F11" s="5">
-        <v>0.488888888888888</v>
+        <v>0.48888888888888798</v>
       </c>
       <c r="G11" s="5">
-        <v>0.478888888888888</v>
+        <v>0.47888888888888798</v>
       </c>
       <c r="H11" s="6">
-        <v>0.569999999999999</v>
+        <v>0.56999999999999895</v>
       </c>
       <c r="I11" s="6">
-        <v>0.505555555555555</v>
+        <v>0.50555555555555498</v>
       </c>
       <c r="J11" s="6">
-        <v>0.555555555555555</v>
+        <v>0.55555555555555503</v>
       </c>
       <c r="K11" s="7">
-        <v>0.5833</v>
-      </c>
-    </row>
-    <row r="12" ht="17.6" spans="1:11">
+        <v>0.58330000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="5">
-        <v>0.821875</v>
+        <v>0.82187500000000002</v>
       </c>
       <c r="C12" s="5">
         <v>0.89</v>
       </c>
       <c r="D12" s="5">
-        <v>0.86875</v>
+        <v>0.86875000000000002</v>
       </c>
       <c r="E12" s="5">
-        <v>0.415625</v>
+        <v>0.41562500000000002</v>
       </c>
       <c r="F12" s="5">
-        <v>0.85625</v>
+        <v>0.85624999999999996</v>
       </c>
       <c r="G12" s="5">
         <v>0.864375</v>
       </c>
       <c r="H12" s="6">
-        <v>0.911875</v>
+        <v>0.91187499999999999</v>
       </c>
       <c r="I12" s="6">
-        <v>0.845</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="J12" s="6">
-        <v>0.86875</v>
+        <v>0.86875000000000002</v>
       </c>
       <c r="K12" s="7">
         <v>0.9194</v>
@@ -3636,7 +6510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="17.6" spans="1:11">
+    <row r="17" spans="1:11" ht="16">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -3681,7 +6555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="17.6" spans="1:11">
+    <row r="18" spans="1:11" ht="16">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
@@ -3726,7 +6600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="17.6" spans="1:11">
+    <row r="19" spans="1:11" ht="16">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -3771,7 +6645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="17.6" spans="1:11">
+    <row r="20" spans="1:11" ht="16">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
@@ -3816,7 +6690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17.6" spans="1:11">
+    <row r="21" spans="1:11" ht="16">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
@@ -3861,7 +6735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="17.6" spans="1:11">
+    <row r="22" spans="1:11" ht="16">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -3906,7 +6780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="17.6" spans="1:11">
+    <row r="23" spans="1:11" ht="16">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
@@ -3951,7 +6825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="17.6" spans="1:11">
+    <row r="24" spans="1:11" ht="16">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
@@ -3996,7 +6870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17.6" spans="1:11">
+    <row r="25" spans="1:11" ht="16">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
@@ -4041,7 +6915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="17.6" spans="1:11">
+    <row r="26" spans="1:11" ht="16">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
@@ -4087,7 +6961,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>